--- a/1105/Debby.xlsx
+++ b/1105/Debby.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lienrueiyu/Desktop/LAB/03collegeproject/01Matlab/1105/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{772BBF9B-16CC-164D-BC3A-9BE44443E9A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99C717B0-C3FB-654B-8847-AF246A80397F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3340" yWindow="2600" windowWidth="27840" windowHeight="16820" xr2:uid="{9D4A684B-518F-A44E-87D9-5AD78979EF79}"/>
+    <workbookView xWindow="3320" yWindow="2600" windowWidth="27840" windowHeight="16820" xr2:uid="{9D4A684B-518F-A44E-87D9-5AD78979EF79}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -332,7 +332,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -374,6 +374,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -714,7 +720,11 @@
   <dimension ref="A1:AJ45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
+    <col min="3" max="3" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="13" width="11" bestFit="1" customWidth="1"/>
+    <col min="20" max="22" width="10.83203125" style="15"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:36" ht="16">
@@ -775,13 +785,13 @@
       <c r="S1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="T1" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="U1" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="V1" s="14" t="s">
         <v>58</v>
       </c>
       <c r="W1" s="3" t="s">
@@ -885,13 +895,13 @@
       <c r="S2" s="4">
         <v>1.957146115308376E-3</v>
       </c>
-      <c r="T2" s="4">
+      <c r="T2" s="14">
         <v>1.0321E-2</v>
       </c>
-      <c r="U2" s="4">
+      <c r="U2" s="14">
         <v>6.8579999999999995E-3</v>
       </c>
-      <c r="V2" s="4">
+      <c r="V2" s="14">
         <v>5.2309999999999995E-3</v>
       </c>
       <c r="W2" s="3">
@@ -995,13 +1005,13 @@
       <c r="S3" s="4">
         <v>8.6064801167492404E-4</v>
       </c>
-      <c r="T3" s="4">
+      <c r="T3" s="14">
         <v>7.6820000000000005E-3</v>
       </c>
-      <c r="U3" s="4">
+      <c r="U3" s="14">
         <v>5.1815000000000003E-3</v>
       </c>
-      <c r="V3" s="4">
+      <c r="V3" s="14">
         <v>4.0547500000000002E-3</v>
       </c>
       <c r="W3" s="3">
@@ -1105,13 +1115,13 @@
       <c r="S4" s="4">
         <v>1.846751652677388E-3</v>
       </c>
-      <c r="T4" s="4">
+      <c r="T4" s="14">
         <v>3.0467500000000002E-2</v>
       </c>
-      <c r="U4" s="4">
+      <c r="U4" s="14">
         <v>1.66175E-2</v>
       </c>
-      <c r="V4" s="4">
+      <c r="V4" s="14">
         <v>7.7000000000000002E-3</v>
       </c>
       <c r="W4" s="3">
@@ -1215,13 +1225,13 @@
       <c r="S5" s="4">
         <v>1.5898113095584644E-4</v>
       </c>
-      <c r="T5" s="4">
+      <c r="T5" s="14">
         <v>1.55725E-3</v>
       </c>
-      <c r="U5" s="4">
+      <c r="U5" s="14">
         <v>1.3749999999999999E-3</v>
       </c>
-      <c r="V5" s="4">
+      <c r="V5" s="14">
         <v>1.1709000000000001E-3</v>
       </c>
       <c r="W5" s="3">
@@ -1325,13 +1335,13 @@
       <c r="S6" s="4">
         <v>1.0132127121192277E-4</v>
       </c>
-      <c r="T6" s="4">
+      <c r="T6" s="14">
         <v>1.3549999999999999E-3</v>
       </c>
-      <c r="U6" s="4">
+      <c r="U6" s="14">
         <v>1.33475E-3</v>
       </c>
-      <c r="V6" s="4">
+      <c r="V6" s="14">
         <v>1.0970000000000001E-3</v>
       </c>
       <c r="W6" s="3">
@@ -1435,13 +1445,13 @@
       <c r="S7" s="4">
         <v>1.6356726445105081E-4</v>
       </c>
-      <c r="T7" s="4">
+      <c r="T7" s="14">
         <v>2.83775E-3</v>
       </c>
-      <c r="U7" s="4">
+      <c r="U7" s="14">
         <v>2.673E-3</v>
       </c>
-      <c r="V7" s="4">
+      <c r="V7" s="14">
         <v>2.23975E-3</v>
       </c>
       <c r="W7" s="3">
@@ -1545,13 +1555,13 @@
       <c r="S8" s="4">
         <v>8.2112686798894411E-4</v>
       </c>
-      <c r="T8" s="4">
+      <c r="T8" s="14">
         <v>8.0226666666666658E-3</v>
       </c>
-      <c r="U8" s="4">
+      <c r="U8" s="14">
         <v>6.4366666666666669E-3</v>
       </c>
-      <c r="V8" s="4">
+      <c r="V8" s="14">
         <v>2.9449999999999997E-3</v>
       </c>
       <c r="W8" s="3">
@@ -1655,13 +1665,13 @@
       <c r="S9" s="4">
         <v>5.5567076583171078E-5</v>
       </c>
-      <c r="T9" s="4">
+      <c r="T9" s="14">
         <v>1.2438000000000002E-3</v>
       </c>
-      <c r="U9" s="4">
+      <c r="U9" s="14">
         <v>1.227E-3</v>
       </c>
-      <c r="V9" s="4">
+      <c r="V9" s="14">
         <v>1.0415000000000001E-3</v>
       </c>
       <c r="W9" s="3">
@@ -1765,13 +1775,13 @@
       <c r="S10" s="4">
         <v>9.2025358823895117E-5</v>
       </c>
-      <c r="T10" s="4">
+      <c r="T10" s="14">
         <v>1.3345000000000002E-3</v>
       </c>
-      <c r="U10" s="4">
+      <c r="U10" s="14">
         <v>1.31025E-3</v>
       </c>
-      <c r="V10" s="4">
+      <c r="V10" s="14">
         <v>1.1264999999999999E-3</v>
       </c>
       <c r="W10" s="3">
@@ -1875,13 +1885,13 @@
       <c r="S11" s="4">
         <v>1.8088371034083401E-4</v>
       </c>
-      <c r="T11" s="4">
+      <c r="T11" s="14">
         <v>5.7794999999999999E-3</v>
       </c>
-      <c r="U11" s="4">
+      <c r="U11" s="14">
         <v>5.0747499999999994E-3</v>
       </c>
-      <c r="V11" s="4">
+      <c r="V11" s="14">
         <v>4.7375000000000004E-3</v>
       </c>
       <c r="W11" s="3">
@@ -1985,13 +1995,13 @@
       <c r="S12" s="4">
         <v>1.4400694427700361E-4</v>
       </c>
-      <c r="T12" s="4">
+      <c r="T12" s="14">
         <v>3.6167499999999997E-3</v>
       </c>
-      <c r="U12" s="4">
+      <c r="U12" s="14">
         <v>3.4762500000000002E-3</v>
       </c>
-      <c r="V12" s="4">
+      <c r="V12" s="14">
         <v>3.1280000000000001E-3</v>
       </c>
       <c r="W12" s="3">
@@ -2095,13 +2105,13 @@
       <c r="S13" s="4">
         <v>5.7668593416752143E-5</v>
       </c>
-      <c r="T13" s="4">
+      <c r="T13" s="14">
         <v>1.5422499999999998E-3</v>
       </c>
-      <c r="U13" s="4">
+      <c r="U13" s="14">
         <v>1.53375E-3</v>
       </c>
-      <c r="V13" s="4">
+      <c r="V13" s="14">
         <v>1.1852499999999999E-3</v>
       </c>
       <c r="W13" s="3">
@@ -2205,13 +2215,13 @@
       <c r="S14" s="4">
         <v>1.3398849453093596E-4</v>
       </c>
-      <c r="T14" s="4">
+      <c r="T14" s="14">
         <v>1.7235000000000002E-3</v>
       </c>
-      <c r="U14" s="4">
+      <c r="U14" s="14">
         <v>1.71675E-3</v>
       </c>
-      <c r="V14" s="4">
+      <c r="V14" s="14">
         <v>1.3319999999999999E-3</v>
       </c>
       <c r="W14" s="3">
@@ -2315,13 +2325,13 @@
       <c r="S15" s="4">
         <v>6.6133072916153867E-5</v>
       </c>
-      <c r="T15" s="4">
+      <c r="T15" s="14">
         <v>1.846E-3</v>
       </c>
-      <c r="U15" s="4">
+      <c r="U15" s="14">
         <v>1.7164999999999999E-3</v>
       </c>
-      <c r="V15" s="4">
+      <c r="V15" s="14">
         <v>1.4840000000000001E-3</v>
       </c>
       <c r="W15" s="3">
@@ -2425,13 +2435,13 @@
       <c r="S16" s="4">
         <v>1.0139485522780065E-4</v>
       </c>
-      <c r="T16" s="4">
+      <c r="T16" s="14">
         <v>4.0882499999999999E-3</v>
       </c>
-      <c r="U16" s="4">
+      <c r="U16" s="14">
         <v>4.0660000000000002E-3</v>
       </c>
-      <c r="V16" s="4">
+      <c r="V16" s="14">
         <v>3.2412499999999998E-3</v>
       </c>
       <c r="W16" s="3">
@@ -2535,13 +2545,13 @@
       <c r="S17" s="4">
         <v>4.484324549658136E-5</v>
       </c>
-      <c r="T17" s="4">
+      <c r="T17" s="14">
         <v>3.3885E-3</v>
       </c>
-      <c r="U17" s="4">
+      <c r="U17" s="14">
         <v>3.3629999999999997E-3</v>
       </c>
-      <c r="V17" s="4">
+      <c r="V17" s="14">
         <v>2.5992500000000004E-3</v>
       </c>
       <c r="W17" s="3">
@@ -2645,13 +2655,13 @@
       <c r="S18" s="4">
         <v>1.6379458680514046E-4</v>
       </c>
-      <c r="T18" s="4">
+      <c r="T18" s="14">
         <v>3.2177500000000001E-3</v>
       </c>
-      <c r="U18" s="4">
+      <c r="U18" s="14">
         <v>3.1844999999999998E-3</v>
       </c>
-      <c r="V18" s="4">
+      <c r="V18" s="14">
         <v>2.4747500000000004E-3</v>
       </c>
       <c r="W18" s="3">
@@ -2755,13 +2765,13 @@
       <c r="S19" s="4">
         <v>1.0116057779589837E-4</v>
       </c>
-      <c r="T19" s="4">
+      <c r="T19" s="14">
         <v>9.3099999999999997E-4</v>
       </c>
-      <c r="U19" s="4">
+      <c r="U19" s="14">
         <v>8.8722499999999995E-4</v>
       </c>
-      <c r="V19" s="4">
+      <c r="V19" s="14">
         <v>8.4447500000000013E-4</v>
       </c>
       <c r="W19" s="3">
@@ -2865,13 +2875,13 @@
       <c r="S20" s="4">
         <v>2.9961141500283329E-4</v>
       </c>
-      <c r="T20" s="4">
+      <c r="T20" s="14">
         <v>4.0010000000000002E-3</v>
       </c>
-      <c r="U20" s="4">
+      <c r="U20" s="14">
         <v>3.5916666666666666E-3</v>
       </c>
-      <c r="V20" s="4">
+      <c r="V20" s="14">
         <v>2.8490000000000004E-3</v>
       </c>
       <c r="W20" s="3">
@@ -2975,13 +2985,13 @@
       <c r="S21" s="4">
         <v>5.4393841563176999E-4</v>
       </c>
-      <c r="T21" s="4">
+      <c r="T21" s="14">
         <v>3.3812500000000001E-3</v>
       </c>
-      <c r="U21" s="4">
+      <c r="U21" s="14">
         <v>3.0427499999999999E-3</v>
       </c>
-      <c r="V21" s="4">
+      <c r="V21" s="14">
         <v>2.5002499999999999E-3</v>
       </c>
       <c r="W21" s="3">
@@ -3085,13 +3095,13 @@
       <c r="S22" s="4">
         <v>1.7931792065119034E-4</v>
       </c>
-      <c r="T22" s="4">
+      <c r="T22" s="14">
         <v>9.8394999999999993E-3</v>
       </c>
-      <c r="U22" s="4">
+      <c r="U22" s="14">
         <v>7.7175000000000004E-3</v>
       </c>
-      <c r="V22" s="4">
+      <c r="V22" s="14">
         <v>4.6802499999999995E-3</v>
       </c>
       <c r="W22" s="3">
@@ -3195,13 +3205,13 @@
       <c r="S23" s="4">
         <v>9.537076770862931E-5</v>
       </c>
-      <c r="T23" s="4">
+      <c r="T23" s="14">
         <v>2.0355E-3</v>
       </c>
-      <c r="U23" s="4">
+      <c r="U23" s="14">
         <v>2.0005000000000001E-3</v>
       </c>
-      <c r="V23" s="4">
+      <c r="V23" s="14">
         <v>1.5947499999999998E-3</v>
       </c>
       <c r="W23" s="3">
@@ -3305,13 +3315,13 @@
       <c r="S24" s="4">
         <v>7.5866110132698054E-5</v>
       </c>
-      <c r="T24" s="4">
+      <c r="T24" s="14">
         <v>2.3219999999999998E-3</v>
       </c>
-      <c r="U24" s="4">
+      <c r="U24" s="14">
         <v>2.2445E-3</v>
       </c>
-      <c r="V24" s="4">
+      <c r="V24" s="14">
         <v>1.8885E-3</v>
       </c>
       <c r="W24" s="3">
@@ -3415,13 +3425,13 @@
       <c r="S25" s="4">
         <v>1.9139923371494109E-4</v>
       </c>
-      <c r="T25" s="4">
+      <c r="T25" s="14">
         <v>2.5659999999999997E-3</v>
       </c>
-      <c r="U25" s="4">
+      <c r="U25" s="14">
         <v>2.4187499999999999E-3</v>
       </c>
-      <c r="V25" s="4">
+      <c r="V25" s="14">
         <v>2.3180000000000002E-3</v>
       </c>
       <c r="W25" s="3">
@@ -3525,13 +3535,13 @@
       <c r="S26" s="4">
         <v>5.5536144386636465E-4</v>
       </c>
-      <c r="T26" s="4">
+      <c r="T26" s="14">
         <v>5.6856666666666661E-3</v>
       </c>
-      <c r="U26" s="4">
+      <c r="U26" s="14">
         <v>4.3403333333333332E-3</v>
       </c>
-      <c r="V26" s="4">
+      <c r="V26" s="14">
         <v>3.1329999999999999E-3</v>
       </c>
       <c r="W26" s="3">
@@ -3635,13 +3645,13 @@
       <c r="S27" s="4">
         <v>4.7224243420796743E-4</v>
       </c>
-      <c r="T27" s="4">
+      <c r="T27" s="14">
         <v>5.6712500000000001E-3</v>
       </c>
-      <c r="U27" s="4">
+      <c r="U27" s="14">
         <v>5.6112499999999999E-3</v>
       </c>
-      <c r="V27" s="4">
+      <c r="V27" s="14">
         <v>4.94175E-3</v>
       </c>
       <c r="W27" s="3">
@@ -3745,13 +3755,13 @@
       <c r="S28" s="4">
         <v>4.4927756825077872E-4</v>
       </c>
-      <c r="T28" s="4">
+      <c r="T28" s="14">
         <v>7.8759999999999993E-3</v>
       </c>
-      <c r="U28" s="4">
+      <c r="U28" s="14">
         <v>5.1419999999999999E-3</v>
       </c>
-      <c r="V28" s="4">
+      <c r="V28" s="14">
         <v>3.3136666666666666E-3</v>
       </c>
       <c r="W28" s="3">
@@ -3855,13 +3865,13 @@
       <c r="S29" s="4">
         <v>5.3998148116393772E-4</v>
       </c>
-      <c r="T29" s="4">
+      <c r="T29" s="14">
         <v>3.0620000000000001E-3</v>
       </c>
-      <c r="U29" s="4">
+      <c r="U29" s="14">
         <v>2.1640000000000001E-3</v>
       </c>
-      <c r="V29" s="4">
+      <c r="V29" s="14">
         <v>1.7780000000000001E-3</v>
       </c>
       <c r="W29" s="3">
@@ -3965,13 +3975,13 @@
       <c r="S30" s="4">
         <v>5.4772255750516647E-5</v>
       </c>
-      <c r="T30" s="4">
+      <c r="T30" s="14">
         <v>2.0625000000000001E-3</v>
       </c>
-      <c r="U30" s="4">
+      <c r="U30" s="14">
         <v>1.9599999999999999E-3</v>
       </c>
-      <c r="V30" s="4">
+      <c r="V30" s="14">
         <v>1.7950000000000002E-3</v>
       </c>
       <c r="W30" s="3">
@@ -4075,13 +4085,13 @@
       <c r="S31" s="4">
         <v>1.2060818103815895E-4</v>
       </c>
-      <c r="T31" s="4">
+      <c r="T31" s="14">
         <v>4.5170000000000002E-3</v>
       </c>
-      <c r="U31" s="4">
+      <c r="U31" s="14">
         <v>3.7353333333333336E-3</v>
       </c>
-      <c r="V31" s="4">
+      <c r="V31" s="14">
         <v>2.9546666666666666E-3</v>
       </c>
       <c r="W31" s="3">
@@ -4185,13 +4195,13 @@
       <c r="S32" s="4">
         <v>1.0503967504392493E-4</v>
       </c>
-      <c r="T32" s="4">
+      <c r="T32" s="14">
         <v>2.7474999999999999E-3</v>
       </c>
-      <c r="U32" s="4">
+      <c r="U32" s="14">
         <v>2.7049999999999999E-3</v>
       </c>
-      <c r="V32" s="4">
+      <c r="V32" s="14">
         <v>2.3400000000000001E-3</v>
       </c>
       <c r="W32" s="3">
@@ -4295,13 +4305,13 @@
       <c r="S33" s="4">
         <v>3.8726907097434636E-5</v>
       </c>
-      <c r="T33" s="4">
+      <c r="T33" s="14">
         <v>8.4176666666666673E-4</v>
       </c>
-      <c r="U33" s="4">
+      <c r="U33" s="14">
         <v>8.3003333333333347E-4</v>
       </c>
-      <c r="V33" s="4">
+      <c r="V33" s="14">
         <v>7.3630000000000006E-4</v>
       </c>
       <c r="W33" s="3">
@@ -4405,13 +4415,13 @@
       <c r="S34" s="4">
         <v>2.2649503305812265E-4</v>
       </c>
-      <c r="T34" s="4">
+      <c r="T34" s="14">
         <v>5.6749999999999995E-3</v>
       </c>
-      <c r="U34" s="4">
+      <c r="U34" s="14">
         <v>5.6000000000000008E-3</v>
       </c>
-      <c r="V34" s="4">
+      <c r="V34" s="14">
         <v>4.7374999999999995E-3</v>
       </c>
       <c r="W34" s="3">
@@ -4515,13 +4525,13 @@
       <c r="S35" s="4">
         <v>2.4931573021639306E-4</v>
       </c>
-      <c r="T35" s="4">
+      <c r="T35" s="14">
         <v>6.9925000000000005E-3</v>
       </c>
-      <c r="U35" s="4">
+      <c r="U35" s="14">
         <v>6.9100000000000003E-3</v>
       </c>
-      <c r="V35" s="4">
+      <c r="V35" s="14">
         <v>6.3024999999999999E-3</v>
       </c>
       <c r="W35" s="3">
@@ -4625,13 +4635,13 @@
       <c r="S36" s="4">
         <v>2.9657601611278953E-5</v>
       </c>
-      <c r="T36" s="4">
+      <c r="T36" s="14">
         <v>7.67E-4</v>
       </c>
-      <c r="U36" s="4">
+      <c r="U36" s="14">
         <v>7.5776666666666664E-4</v>
       </c>
-      <c r="V36" s="4">
+      <c r="V36" s="14">
         <v>6.828666666666666E-4</v>
       </c>
       <c r="W36" s="3">
@@ -4735,13 +4745,13 @@
       <c r="S37" s="4">
         <v>2.6993764712120698E-4</v>
       </c>
-      <c r="T37" s="4">
+      <c r="T37" s="14">
         <v>5.7603333333333335E-3</v>
       </c>
-      <c r="U37" s="4">
+      <c r="U37" s="14">
         <v>5.7320000000000001E-3</v>
       </c>
-      <c r="V37" s="4">
+      <c r="V37" s="14">
         <v>5.0163333333333336E-3</v>
       </c>
       <c r="W37" s="3">
@@ -4845,13 +4855,13 @@
       <c r="S38" s="4">
         <v>1.2675435561221009E-4</v>
       </c>
-      <c r="T38" s="4">
+      <c r="T38" s="14">
         <v>5.1425000000000004E-3</v>
       </c>
-      <c r="U38" s="4">
+      <c r="U38" s="14">
         <v>4.9849999999999998E-3</v>
       </c>
-      <c r="V38" s="4">
+      <c r="V38" s="14">
         <v>4.6375000000000001E-3</v>
       </c>
       <c r="W38" s="3">
@@ -4955,13 +4965,13 @@
       <c r="S39" s="4">
         <v>3.8792138378800425E-4</v>
       </c>
-      <c r="T39" s="4">
+      <c r="T39" s="14">
         <v>2.7973333333333335E-3</v>
       </c>
-      <c r="U39" s="4">
+      <c r="U39" s="14">
         <v>2.5569999999999998E-3</v>
       </c>
-      <c r="V39" s="4">
+      <c r="V39" s="14">
         <v>2.1383333333333337E-3</v>
       </c>
       <c r="W39" s="3">
@@ -5065,13 +5075,13 @@
       <c r="S40" s="4">
         <v>2.6742273027300175E-4</v>
       </c>
-      <c r="T40" s="4">
+      <c r="T40" s="14">
         <v>4.0305000000000002E-3</v>
       </c>
-      <c r="U40" s="4">
+      <c r="U40" s="14">
         <v>3.8982499999999998E-3</v>
       </c>
-      <c r="V40" s="4">
+      <c r="V40" s="14">
         <v>3.4099999999999998E-3</v>
       </c>
       <c r="W40" s="3">
@@ -5175,13 +5185,13 @@
       <c r="S41" s="4">
         <v>7.4790262289507544E-5</v>
       </c>
-      <c r="T41" s="4">
+      <c r="T41" s="14">
         <v>9.0943333333333334E-4</v>
       </c>
-      <c r="U41" s="4">
+      <c r="U41" s="14">
         <v>8.8923333333333339E-4</v>
       </c>
-      <c r="V41" s="4">
+      <c r="V41" s="14">
         <v>7.938E-4</v>
       </c>
       <c r="W41" s="3">
@@ -5285,13 +5295,13 @@
       <c r="S42" s="4">
         <v>1.1432544190453261E-4</v>
       </c>
-      <c r="T42" s="4">
+      <c r="T42" s="14">
         <v>1.0689E-3</v>
       </c>
-      <c r="U42" s="4">
+      <c r="U42" s="14">
         <v>1.0074999999999999E-3</v>
       </c>
-      <c r="V42" s="4">
+      <c r="V42" s="14">
         <v>9.7380000000000003E-4</v>
       </c>
       <c r="W42" s="3">
@@ -5395,13 +5405,13 @@
       <c r="S43" s="4">
         <v>1.9800757561265183E-4</v>
       </c>
-      <c r="T43" s="4">
+      <c r="T43" s="14">
         <v>1.4455000000000002E-3</v>
       </c>
-      <c r="U43" s="4">
+      <c r="U43" s="14">
         <v>1.3205000000000001E-3</v>
       </c>
-      <c r="V43" s="4">
+      <c r="V43" s="14">
         <v>1.2355000000000001E-3</v>
       </c>
       <c r="W43" s="3">
@@ -5505,13 +5515,13 @@
       <c r="S44" s="4">
         <v>2.0435385976291207E-4</v>
       </c>
-      <c r="T44" s="4">
+      <c r="T44" s="14">
         <v>2.5875E-3</v>
       </c>
-      <c r="U44" s="4">
+      <c r="U44" s="14">
         <v>2.5154999999999999E-3</v>
       </c>
-      <c r="V44" s="4">
+      <c r="V44" s="14">
         <v>2.2630000000000003E-3</v>
       </c>
       <c r="W44" s="3">
@@ -5615,13 +5625,13 @@
       <c r="S45" s="3">
         <v>1.1120551545074853E-4</v>
       </c>
-      <c r="T45" s="4">
+      <c r="T45" s="14">
         <v>1.6649999999999998E-3</v>
       </c>
-      <c r="U45" s="4">
+      <c r="U45" s="14">
         <v>1.5550000000000002E-3</v>
       </c>
-      <c r="V45" s="4">
+      <c r="V45" s="14">
         <v>1.4375E-3</v>
       </c>
       <c r="W45" s="3">
